--- a/core/public/static/test-files/test.xlsx
+++ b/core/public/static/test-files/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="色彩" sheetId="1" r:id="rId1"/>
@@ -43,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>抵押贷款</t>
   </si>
@@ -134,20 +156,24 @@
   </si>
   <si>
     <t>公式求和</t>
+  </si>
+  <si>
+    <t>保留两位小数</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="\¥#,##0"/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="\¥#,##0"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="37">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -163,13 +189,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="28"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -177,6 +196,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="18"/>
       <color theme="0"/>
       <name val="等线"/>
@@ -198,13 +224,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="9" tint="0.399975585192419"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="24"/>
       <color theme="0"/>
       <name val="等线"/>
@@ -213,20 +232,6 @@
     </font>
     <font>
       <sz val="20"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="0"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -262,14 +267,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="5"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="22"/>
       <color theme="0"/>
       <name val="等线"/>
@@ -367,14 +364,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
@@ -456,7 +445,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="65">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,6 +460,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -483,12 +478,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -705,48 +694,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -771,42 +718,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -817,37 +734,28 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1121,174 +1029,171 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="36" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="37" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1297,37 +1202,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1336,40 +1238,37 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="9" borderId="5" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="9" borderId="6" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="15" fillId="9" borderId="8" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="8" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="9" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="9" borderId="5" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="9" borderId="6" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="9" borderId="10" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="11" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="9" borderId="5" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="9" borderId="6" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="11" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="12" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="9" borderId="13" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="14" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
@@ -1387,7 +1286,7 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
@@ -1405,7 +1304,7 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1">
@@ -1423,7 +1322,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1">
@@ -1441,7 +1340,7 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1">
@@ -1459,7 +1358,7 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1667,11 +1566,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Mortgage calculator" pivot="0" count="2" xr9:uid="{094B5181-4FCE-413F-9653-FD488921BBB4}">
+    <tableStyle name="Mortgage calculator" pivot="0" count="2" xr9:uid="{E097D53E-29D9-4E3F-A316-540D95553A1D}">
       <tableStyleElement type="wholeTable" dxfId="4"/>
       <tableStyleElement type="lastColumn" dxfId="3"/>
     </tableStyle>
-    <tableStyle name="Mortgage calculator 2" pivot="0" count="2" xr9:uid="{6FFC53B7-4E74-4858-801B-D8F62C5F84A5}">
+    <tableStyle name="Mortgage calculator 2" pivot="0" count="2" xr9:uid="{D43734D0-64A1-4DE1-9B0B-56AA6D61A415}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="lastColumn" dxfId="5"/>
     </tableStyle>
@@ -2034,189 +1933,189 @@
       <c r="G1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="15"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" ht="31" customHeight="1" spans="1:9">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="18" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="20"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:9">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="G3" s="23" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="G3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="25"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:9">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24">
         <v>3000000</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="G4" s="28" t="s">
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="G4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="30" t="s">
+      <c r="H4" s="26"/>
+      <c r="I4" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="G5" s="32" t="s">
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="G5" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="34" t="s">
+      <c r="H5" s="30"/>
+      <c r="I5" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="27">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24">
         <v>360</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="G6" s="32" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="G6" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="33"/>
-      <c r="I6" s="34" t="s">
+      <c r="H6" s="30"/>
+      <c r="I6" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="G7" s="32" t="s">
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="G7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="34" t="s">
+      <c r="H7" s="30"/>
+      <c r="I7" s="31" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="35">
+      <c r="B8" s="23"/>
+      <c r="C8" s="32">
         <v>44983</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="G8" s="36" t="s">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="G8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="37"/>
-      <c r="I8" s="38">
+      <c r="H8" s="34"/>
+      <c r="I8" s="35">
         <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43"/>
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
       <c r="G12" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="44"/>
+      <c r="I12" s="41"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="45"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="49"/>
-      <c r="G13" s="50" t="s">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="46"/>
+      <c r="G13" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="51"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
-      <c r="G14" s="56" t="s">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="G14" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="57"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="61"/>
-      <c r="G15" s="62" t="s">
+      <c r="A15" s="54"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="58"/>
+      <c r="G15" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="63"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="67"/>
-      <c r="G16" s="68" t="s">
+      <c r="A16" s="60"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="64"/>
+      <c r="G16" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2257,18 +2156,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="29" customHeight="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="6"/>
@@ -2302,8 +2201,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16.8333333333333" customWidth="1"/>
@@ -2315,26 +2214,77 @@
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1">
         <v>1</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>2</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="62" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <f>SUM(B1:D1)</f>
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="18" spans="1:4">
+      <c r="B5" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="4">
+        <v>88.689</v>
+      </c>
+    </row>
+    <row r="6" ht="18" spans="1:4">
+      <c r="B6" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>83.48</v>
+      </c>
+    </row>
+    <row r="7" ht="18" spans="1:4">
+      <c r="B7" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="C7" s="4">
+        <v>84.05</v>
+      </c>
+    </row>
+    <row r="8" ht="18" spans="1:4">
+      <c r="B8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="4">
+        <v>89.75</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="1:4">
+      <c r="B9" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="C9" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:4">
+      <c r="C10" s="4" cm="1">
+        <f t="array" ref="C10">SUMPRODUCT(C5:C9,B5:B9)</f>
+        <v>89.5274</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
